--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122343271</v>
+        <v>122343359</v>
       </c>
       <c r="B16" t="n">
-        <v>56619</v>
+        <v>57553</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102118</v>
+        <v>102623</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666470</v>
+        <v>666017</v>
       </c>
       <c r="R16" t="n">
-        <v>6612355</v>
+        <v>6612959</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122343359</v>
+        <v>122343271</v>
       </c>
       <c r="B17" t="n">
-        <v>57553</v>
+        <v>56619</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102623</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666017</v>
+        <v>666470</v>
       </c>
       <c r="R17" t="n">
-        <v>6612959</v>
+        <v>6612355</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>122343359</v>
       </c>
       <c r="B16" t="n">
-        <v>57553</v>
+        <v>57558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>122343271</v>
       </c>
       <c r="B17" t="n">
-        <v>56619</v>
+        <v>56624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122343359</v>
+        <v>122343271</v>
       </c>
       <c r="B16" t="n">
-        <v>57558</v>
+        <v>56624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102623</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666017</v>
+        <v>666470</v>
       </c>
       <c r="R16" t="n">
-        <v>6612959</v>
+        <v>6612355</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122343271</v>
+        <v>122343359</v>
       </c>
       <c r="B17" t="n">
-        <v>56624</v>
+        <v>57558</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102623</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666470</v>
+        <v>666017</v>
       </c>
       <c r="R17" t="n">
-        <v>6612355</v>
+        <v>6612959</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2298,11 +2298,6 @@
       <c r="E16" t="n">
         <v>102118</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Caprimulgus europaeus</t>
@@ -2408,11 +2403,6 @@
       </c>
       <c r="E17" t="n">
         <v>102623</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Trädlärka</t>
-        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>122343271</v>
       </c>
       <c r="B16" t="n">
-        <v>56624</v>
+        <v>56628</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,6 +2297,11 @@
       </c>
       <c r="E16" t="n">
         <v>102118</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2389,7 +2394,7 @@
         <v>122343359</v>
       </c>
       <c r="B17" t="n">
-        <v>57558</v>
+        <v>57562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,6 +2408,11 @@
       </c>
       <c r="E17" t="n">
         <v>102623</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122343271</v>
+        <v>122343359</v>
       </c>
       <c r="B16" t="n">
-        <v>56628</v>
+        <v>57562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102118</v>
+        <v>102623</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666470</v>
+        <v>666017</v>
       </c>
       <c r="R16" t="n">
-        <v>6612355</v>
+        <v>6612959</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122343359</v>
+        <v>122343271</v>
       </c>
       <c r="B17" t="n">
-        <v>57562</v>
+        <v>56628</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102623</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666017</v>
+        <v>666470</v>
       </c>
       <c r="R17" t="n">
-        <v>6612959</v>
+        <v>6612355</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122343359</v>
+        <v>122343271</v>
       </c>
       <c r="B16" t="n">
-        <v>57562</v>
+        <v>56628</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102623</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666017</v>
+        <v>666470</v>
       </c>
       <c r="R16" t="n">
-        <v>6612959</v>
+        <v>6612355</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122343271</v>
+        <v>122343359</v>
       </c>
       <c r="B17" t="n">
-        <v>56628</v>
+        <v>57562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102623</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666470</v>
+        <v>666017</v>
       </c>
       <c r="R17" t="n">
-        <v>6612355</v>
+        <v>6612959</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>122343359</v>
       </c>
       <c r="B16" t="n">
-        <v>57562</v>
+        <v>57563</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>122343271</v>
       </c>
       <c r="B17" t="n">
-        <v>56628</v>
+        <v>56629</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122343359</v>
+        <v>122343271</v>
       </c>
       <c r="B16" t="n">
-        <v>57563</v>
+        <v>56629</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102623</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666017</v>
+        <v>666470</v>
       </c>
       <c r="R16" t="n">
-        <v>6612959</v>
+        <v>6612355</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122343271</v>
+        <v>122343359</v>
       </c>
       <c r="B17" t="n">
-        <v>56629</v>
+        <v>57563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102623</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666470</v>
+        <v>666017</v>
       </c>
       <c r="R17" t="n">
-        <v>6612355</v>
+        <v>6612959</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2280,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122343271</v>
+        <v>122343359</v>
       </c>
       <c r="B16" t="n">
-        <v>56629</v>
+        <v>57563</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102118</v>
+        <v>102623</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666470</v>
+        <v>666017</v>
       </c>
       <c r="R16" t="n">
-        <v>6612355</v>
+        <v>6612959</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122343359</v>
+        <v>122343271</v>
       </c>
       <c r="B17" t="n">
-        <v>57563</v>
+        <v>56629</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102623</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666017</v>
+        <v>666470</v>
       </c>
       <c r="R17" t="n">
-        <v>6612959</v>
+        <v>6612355</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,132 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122787262</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58183</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Arlanda Södra, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>666012</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612914</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skånela</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60838-2021 artfynd.xlsx
+++ b/artfynd/A 60838-2021 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>122787262</v>
       </c>
       <c r="B18" t="n">
-        <v>58183</v>
+        <v>58186</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
